--- a/4523 JP.xlsx
+++ b/4523 JP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549D0BBE-BE93-490C-BB6A-571C4C8225FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71774C88-7F08-4E3F-B4B1-99C2D1FD8476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27015" yWindow="750" windowWidth="26490" windowHeight="19650" activeTab="1" xr2:uid="{946D9990-1487-43B7-9903-781AF13E65FA}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{946D9990-1487-43B7-9903-781AF13E65FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
   <si>
     <t>Price JPY</t>
   </si>
@@ -352,6 +352,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -879,17 +882,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DC82C6-A62B-41C1-B0EB-2FB45B1695A0}">
   <dimension ref="B2:L29"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
+    <col min="1" max="1" width="3.54296875" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
@@ -908,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6022</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+        <v>4828</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
@@ -929,13 +932,13 @@
         <v>1</v>
       </c>
       <c r="K3" s="11">
-        <v>286.34741200000002</v>
+        <v>281.890197</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
@@ -948,11 +951,11 @@
       </c>
       <c r="K4" s="11">
         <f>+K2*K3</f>
-        <v>1724384.115064</v>
+        <v>1360965.871116</v>
       </c>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
@@ -964,14 +967,14 @@
         <v>3</v>
       </c>
       <c r="K5" s="11">
-        <f>303935+59620</f>
-        <v>363555</v>
+        <f>245423+892+62412</f>
+        <v>308727</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
@@ -986,14 +989,14 @@
         <v>4</v>
       </c>
       <c r="K6" s="11">
-        <f>47548+134786+16608+39481</f>
-        <v>238423</v>
+        <f>51304+134777+16264</f>
+        <v>202345</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
@@ -1006,10 +1009,10 @@
       </c>
       <c r="K7" s="11">
         <f>+K4-K5+K6</f>
-        <v>1599252.115064</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>1254583.871116</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1018,7 +1021,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1030,7 +1033,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1039,7 +1042,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1048,7 +1051,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>68</v>
       </c>
@@ -1060,7 +1063,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>70</v>
       </c>
@@ -1069,7 +1072,7 @@
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>71</v>
       </c>
@@ -1081,7 +1084,7 @@
       </c>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>72</v>
       </c>
@@ -1090,7 +1093,7 @@
       </c>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>25</v>
       </c>
@@ -1102,7 +1105,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="8"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1110,7 +1113,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
@@ -1119,33 +1122,33 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="3"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1153,17 +1156,17 @@
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
         <v>17</v>
       </c>
@@ -1176,26 +1179,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF92CCD9-B450-44A6-A5E5-E1617EC33FE0}">
   <dimension ref="A1:V44"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="12"/>
-    <col min="5" max="5" width="10.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.140625" style="12"/>
-    <col min="9" max="9" width="10.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="9.140625" style="12"/>
-    <col min="13" max="13" width="10.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="9.140625" style="12"/>
-    <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.1796875" style="12"/>
+    <col min="5" max="5" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="9.1796875" style="12"/>
+    <col min="9" max="9" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="9.1796875" style="12"/>
+    <col min="13" max="13" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="9.1796875" style="12"/>
+    <col min="17" max="17" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C2" s="13">
         <v>44012</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="12" t="s">
         <v>32</v>
       </c>
@@ -1310,7 +1313,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>56</v>
       </c>
@@ -1332,7 +1335,7 @@
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
         <v>57</v>
       </c>
@@ -1354,7 +1357,7 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>58</v>
       </c>
@@ -1376,7 +1379,7 @@
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>59</v>
       </c>
@@ -1398,7 +1401,7 @@
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
         <v>60</v>
       </c>
@@ -1420,7 +1423,7 @@
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>61</v>
       </c>
@@ -1442,7 +1445,7 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>62</v>
       </c>
@@ -1464,7 +1467,7 @@
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
@@ -1479,7 +1482,7 @@
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>90</v>
       </c>
@@ -1511,7 +1514,7 @@
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
         <v>78</v>
       </c>
@@ -1533,7 +1536,7 @@
       <c r="N13" s="14"/>
       <c r="O13" s="14"/>
     </row>
-    <row r="14" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>95</v>
       </c>
@@ -1555,7 +1558,7 @@
       <c r="N14" s="14"/>
       <c r="O14" s="14"/>
     </row>
-    <row r="15" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
         <v>79</v>
       </c>
@@ -1577,7 +1580,7 @@
       <c r="N15" s="14"/>
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
         <v>91</v>
       </c>
@@ -1599,7 +1602,7 @@
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
     </row>
-    <row r="17" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
         <v>96</v>
       </c>
@@ -1621,7 +1624,7 @@
       <c r="N17" s="14"/>
       <c r="O17" s="14"/>
     </row>
-    <row r="18" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
         <v>92</v>
       </c>
@@ -1643,7 +1646,7 @@
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
         <v>80</v>
       </c>
@@ -1665,7 +1668,7 @@
       <c r="N19" s="14"/>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
         <v>81</v>
       </c>
@@ -1687,7 +1690,7 @@
       <c r="N20" s="14"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
         <v>82</v>
       </c>
@@ -1709,7 +1712,7 @@
       <c r="N21" s="14"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
         <v>83</v>
       </c>
@@ -1731,7 +1734,7 @@
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
         <v>84</v>
       </c>
@@ -1753,7 +1756,7 @@
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
         <v>85</v>
       </c>
@@ -1775,7 +1778,7 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
         <v>86</v>
       </c>
@@ -1797,7 +1800,7 @@
       <c r="N25" s="14"/>
       <c r="O25" s="14"/>
     </row>
-    <row r="26" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="11" t="s">
         <v>87</v>
       </c>
@@ -1819,7 +1822,7 @@
       <c r="N26" s="14"/>
       <c r="O26" s="14"/>
     </row>
-    <row r="27" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="11" t="s">
         <v>88</v>
       </c>
@@ -1841,7 +1844,7 @@
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
     </row>
-    <row r="28" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
         <v>93</v>
       </c>
@@ -1863,7 +1866,7 @@
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
     </row>
-    <row r="29" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="11" t="s">
         <v>94</v>
       </c>
@@ -1885,7 +1888,7 @@
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
     </row>
-    <row r="30" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
         <v>89</v>
       </c>
@@ -1907,7 +1910,7 @@
       <c r="N30" s="14"/>
       <c r="O30" s="14"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="11" t="s">
         <v>31</v>
@@ -1940,7 +1943,7 @@
         <v>187497</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
         <v>44</v>
@@ -1963,7 +1966,7 @@
         <v>139272</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="11" t="s">
         <v>45</v>
@@ -1986,7 +1989,7 @@
         <v>48225</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="11" t="s">
         <v>48</v>
@@ -2009,7 +2012,7 @@
         <v>272970</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="11" t="s">
         <v>49</v>
@@ -2032,7 +2035,7 @@
         <v>121403</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="11" t="s">
         <v>47</v>
@@ -2055,7 +2058,7 @@
         <v>394373</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11" t="s">
         <v>46</v>
@@ -2078,7 +2081,7 @@
         <v>-346148</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B39" s="11" t="s">
         <v>55</v>
       </c>
@@ -2091,7 +2094,7 @@
         <v>5038</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B40" s="11" t="s">
         <v>54</v>
       </c>
@@ -2104,7 +2107,7 @@
         <v>-341110</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
         <v>53</v>
       </c>
@@ -2117,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>52</v>
       </c>
@@ -2130,7 +2133,7 @@
         <v>-341110</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>51</v>
       </c>
@@ -2139,7 +2142,7 @@
         <v>-1188.5365853658536</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>50</v>
       </c>
